--- a/questions.xlsx
+++ b/questions.xlsx
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -433,17 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,29 +495,29 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Phương châm cơ bản trong công tác phòng cháy và chữa cháy là gì?</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Phòng ngừa là chính</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Chữa cháy là chính</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Xử phạt là chính</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Trang bị là chính</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật PCCC &amp; CNCH 2024, hoạt động PCCC &amp; CNCH trên lãnh thổ Việt Nam được thực hiện theo quy định nào?</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật này và pháp luật có liên quan</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ theo Luật này</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ theo điều ước quốc tế</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Theo quy định của từng địa phương</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -522,35 +525,39 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Điều 3 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Khi phát hiện cháy, việc cần làm đầu tiên là gì?</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Báo cháy ngay</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Chờ chỉ huy</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Rời khỏi hiện trường không báo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tự ý ngắt toàn bộ điện khu vực khác</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Hoạt động phòng cháy, chữa cháy rừng được áp dụng theo pháp luật nào?</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Pháp luật về lâm nghiệp</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Pháp luật về giao thông</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Pháp luật về xây dựng</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Pháp luật về lao động</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -558,35 +565,39 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Điều 3 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Bình chữa cháy xách tay thường dùng ban đầu để xử lý đám cháy ở giai đoạn nào?</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mới phát sinh, quy mô nhỏ</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Đã cháy lan lớn</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cháy toàn bộ công trình</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ dùng ngoài trời</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Một nguyên tắc cơ bản trong hoạt động PCCC &amp; CNCH theo Luật 2024 là gì?</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Chủ động phòng ngừa, lấy phòng ngừa là chính</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tập trung chữa cháy khi có cháy</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ huy động lực lượng chuyên nghiệp</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ ưu tiên cứu tài sản</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -594,79 +605,1891 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Điều 5 khoản 3. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Trong file Excel ngân hàng đề, cột Correct phải nhập giá trị nào?</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nội dung đáp án đúng</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Số thứ tự đáp án</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Một trong 4 ký tự A/B/C/D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Có thể để trống</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Theo nguyên tắc của Luật 2024, khi xảy ra cháy/tai nạn, ưu tiên hàng đầu là gì?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Ưu tiên cứu người, cứu tài sản</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ưu tiên bảo vệ hiện trường</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Ưu tiên bảo vệ phương tiện chữa cháy</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ưu tiên cứu tài sản trước, cứu người sau</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Điều 5 khoản 5. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi thí sinh trong hệ thống này sẽ làm bao nhiêu câu hỏi?</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10 câu</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15 câu</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20 câu</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30 câu</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, số điện thoại báo cháy và báo tình huống cứu nạn, cứu hộ thống nhất toàn quốc là số nào?</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Điều 6 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Người phát hiện cháy/tình huống CNCH phải làm gì theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Báo ngay cho lực lượng PCCC &amp; CNCH/cơ quan Công an/UBND cấp xã nơi gần nhất</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chờ lực lượng chuyên trách đến</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ báo cho tổ dân phố</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Tự xử lý xong mới báo</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Điều 6 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, Bộ nào là cơ quan đầu mối giúp Chính phủ thống nhất quản lý nhà nước về PCCC &amp; CNCH?</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Bộ Công an</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Bộ Xây dựng</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Bộ Thông tin và Truyền thông</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Điều 7 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, “Ngày toàn dân phòng cháy, chữa cháy và cứu nạn, cứu hộ” là ngày nào?</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>01/7 hằng năm</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>04/10 hằng năm</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>30/4 hằng năm</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>02/9 hằng năm</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Điều 12. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Luật số 55/2024/QH15 (Luật PCCC &amp; CNCH) có hiệu lực thi hành từ ngày nào?</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>29/11/2024</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Ngày hiệu lực 01/07/2025. Nguồn: https://congbao.chinhphu.vn/van-ban/luat-so-55-2024-qh15-43594.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Luật Phòng cháy, chữa cháy và cứu nạn, cứu hộ năm 2024 có số, ký hiệu là gì?</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>54/2024/QH15</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>55/2024/QH15</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>56/2024/QH15</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>55/2025/QH15</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Số, ký hiệu: 55/2024/QH15. Nguồn: https://congbao.chinhphu.vn/van-ban/luat-so-55-2024-qh15-43594.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Hành vi nào sau đây bị nghiêm cấm theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Cố ý gây cháy, nổ hoặc kích động người khác gây cháy, nổ</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Báo cháy bằng điện thoại</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Tập huấn PCCC cho người lao động</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Trang bị bình chữa cháy tại nhà</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Điều 14 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Hành vi nào bị nghiêm cấm theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Xúc phạm, đe dọa, cản trở, chống đối lực lượng làm nhiệm vụ PCCC &amp; CNCH</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Tham gia chữa cháy khi được huy động</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Tổ chức thực tập phương án chữa cháy</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng phương tiện PCCC</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Điều 14 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, hành vi nào bị nghiêm cấm?</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Chiếm đoạt, hủy hoại hoặc cố ý làm hư hỏng phương tiện PCCC &amp; CNCH</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Lắp đặt dây dẫn điện đúng quy chuẩn</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Bố trí lối thoát nạn</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Khai báo cập nhật dữ liệu PCCC theo lộ trình</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Điều 14 khoản 10. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, hành vi nào bị nghiêm cấm?</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Cản trở lối thoát nạn hoặc làm mất tác dụng của lối/đường thoát nạn, ngăn cháy lan</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Bố trí biển chỉ dẫn lối thoát nạn</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Trang bị thiết bị báo cháy</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Tập huấn kỹ năng thoát nạn</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Điều 14 khoản 10. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, hành vi nào bị nghiêm cấm?</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Lấn chiếm, bố trí vật cản gây cản trở hoạt động của phương tiện chữa cháy, CNCH cơ giới</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Bố trí khoảng trống cho xe chữa cháy</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Bố trí điểm lấy nước chữa cháy</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Đảm bảo an toàn điện trong sinh hoạt</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Điều 14 khoản 11. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, PCCC &amp; CNCH là trách nhiệm của đối tượng nào?</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ lực lượng Cảnh sát PCCC &amp; CNCH</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ UBND các cấp</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan, tổ chức, hộ gia đình, cá nhân hoạt động/sinh sống trên lãnh thổ Việt Nam</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ người đứng đầu cơ sở</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Điều 8 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Công dân từ đủ 18 tuổi trở lên, đủ sức khỏe có trách nhiệm gì theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Tham gia Đội PCCC &amp; CNCH cơ sở/chuyên ngành hoặc Đội dân phòng khi có yêu cầu</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc trực 24/7 tại trụ sở PCCC</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần học lý thuyết PCCC</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Không có trách nhiệm gì</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Điều 8 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Người đứng đầu cơ sở có trách nhiệm nào sau đây theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Tổ chức huấn luyện, bồi dưỡng nghiệp vụ PCCC &amp; CNCH cho đối tượng thuộc phạm vi quản lý</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ báo cáo khi có cháy lớn</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ mua bảo hiểm cháy nổ</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ ký cam kết an toàn</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Điều 8 khoản 3 điểm a. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Người đứng đầu cơ sở có trách nhiệm nào sau đây theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Ban hành (hoặc tham mưu ban hành) nội quy PCCC &amp; CNCH</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Cấm mọi hoạt động kiểm tra</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ giao khoán cho bảo vệ</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Không cần lập hồ sơ PCCC</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Điều 8 khoản 3 điểm c. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Cá nhân có trách nhiệm nào sau đây theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Chấp hành nội quy/biện pháp/yêu cầu PCCC &amp; CNCH của cơ quan, tổ chức hoặc người có thẩm quyền</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ chấp hành khi có cháy</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Không cần tìm hiểu kỹ năng thoát nạn</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Tự ý di chuyển phương tiện PCCC</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Điều 8 khoản 7 điểm a. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Nhà ở (loại không thuộc khoản 3,4 Điều 20) phải bảo đảm điều kiện nào về thoát nạn?</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Có lối thoát nạn/lối ra khẩn cấp hoặc lối đi bảo đảm việc thoát nạn</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần có bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần có biển chỉ dẫn</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Không cần lối thoát nạn</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Điều 20 khoản 2 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Nhà ở phải bố trí bếp đun nấu, nơi thờ cúng, đốt vàng mã như thế nào?</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Bảo đảm an toàn, không để vật/chất dễ cháy nổ gần nguồn lửa, nguồn nhiệt</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Đặt sát vật liệu dễ cháy để tiện sử dụng</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Không có yêu cầu</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần đặt ngoài ban công</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Điều 20 khoản 1 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Nhà ở kết hợp sản xuất, kinh doanh phải bảo đảm điều kiện nào sau đây?</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Có biển cấm/biển báo/biển chỉ dẫn theo quy định</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Không cần biển báo nếu diện tích nhỏ</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần báo cho tổ dân phố</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần có hệ thống camera</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Điều 21 khoản 1 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Nhà ở kết hợp sản xuất, kinh doanh hàng hóa có nguy cơ cháy, nổ phải có giải pháp gì?</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Giải pháp ngăn cách hoặc ngăn cháy với khu vực để ở</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần thêm quạt thông gió</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần thêm đèn chiếu sáng</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Không cần ngăn cách</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Điều 21 khoản 1 điểm c. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Nhà ở kết hợp sản xuất, kinh doanh hàng hóa nguy hiểm về cháy, nổ phải bảo đảm điều kiện nào sau đây?</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Không bố trí chỗ ngủ trong khu vực sản xuất, kinh doanh</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Bố trí chỗ ngủ ngay trong kho hàng</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần ngủ gần cửa thoát hiểm</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Không có quy định</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Điều 21 khoản 2 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Cơ sở phải bảo đảm điều kiện nào sau đây về phòng cháy?</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Trang bị thiết bị truyền tin báo cháy kết nối CSDL PCCC &amp; CNCH theo lộ trình và khai báo/cập nhật dữ liệu</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần dán số điện thoại 114</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần có bảo vệ trực</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Không cần khai báo/cập nhật dữ liệu</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Điều 23 khoản 1 điểm c. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, đối tượng kiểm tra về PCCC bao gồm những gì?</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Cơ sở; nhà ở/nhà ở kết hợp SXKD; phương tiện giao thông; công trình đang thi công</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cơ sở có nguy hiểm cháy nổ</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ nhà ở</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ công trình đang thi công</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Điều 11 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Người đứng đầu cơ sở/chủ phương tiện giao thông thuộc diện quy định có trách nhiệm gì về phương án?</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Tổ chức xây dựng và thực tập phương án chữa cháy, CNCH sử dụng lực lượng, phương tiện tại chỗ</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần treo nội quy</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần mua thêm bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Không cần thực tập phương án</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Điều 10 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Thông tin báo cháy/báo tình huống CNCH có thể được thực hiện bằng cách nào theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Hiệu lệnh, điện thoại, tín hiệu từ thiết bị truyền tin báo cháy, hoặc báo trực tiếp</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ bằng văn bản</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ bằng email</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ bằng tin nhắn SMS</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Điều 6 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Theo quy định chuyển tiếp, việc trang bị thiết bị truyền tin báo cháy kết nối CSDL theo lộ trình (Điều 20(5), Điều 23(1)(c)) thực hiện chậm nhất từ ngày nào?</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2027</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>04/10/2027</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Điều 55 khoản 4 (quy định chuyển tiếp). Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Trong lắp đặt, sử dụng điện cho sinh hoạt, yêu cầu nào sau đây đúng theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Thường xuyên kiểm tra, kịp thời sửa chữa/thay thế dây dẫn, thiết bị điện không bảo đảm an toàn về PCCC</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ kiểm tra khi mất điện</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Không cần kiểm tra định kỳ</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ thay thiết bị khi cháy xảy ra</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 1 điểm c. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Đơn vị bán lẻ điện khi đấu nối điện sinh hoạt có trách nhiệm gì?</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Tư vấn việc lắp đặt, sử dụng hệ thống/thiết bị điện để bảo đảm an toàn PCCC</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Không có trách nhiệm</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ thu tiền điện</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ kiểm tra công tơ</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 1 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, người phát hiện cháy và người ở gần nơi xảy ra cháy có trách nhiệm gì?</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Tham gia chữa cháy trong điều kiện, khả năng cho phép</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ đứng quan sát</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ quay phim hiện trường</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ chờ lực lượng chuyên nghiệp</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Điều 25 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, lực lượng/ phương tiện/ tài sản được huy động chữa cháy phải được xử lý thế nào sau khi kết thúc chữa cháy?</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Hoàn trả ngay; nếu mất/hư hỏng do huy động trực tiếp gây ra thì được bồi thường</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Giữ lại vĩnh viễn</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ hoàn trả nếu có yêu cầu bằng văn bản</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Không hoàn trả</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Điều 26 khoản 3. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Nguồn nước chữa cháy theo Luật 2024 có thể lấy từ đâu?</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Trụ nước chữa cháy; hệ thống cấp nước; bồn/bể; ao/hồ/sông/suối/kênh hoặc nguồn sẵn có khác</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ từ hồ tự nhiên</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ từ trụ nước chữa cháy</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ từ xe bồn</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Chi phí sử dụng nước từ hệ thống cấp nước tập trung do cơ quan Công an sử dụng để chữa cháy và thực tập phương án được chi trả từ nguồn nào?</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Ngân sách nhà nước</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Quỹ phúc lợi doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Đóng góp tự nguyện của người dân</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Không có quy định</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, ai là người chỉ huy chữa cháy khi lực lượng Công an nhân dân chưa đến và cháy xảy ra tại cơ sở?</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Người đứng đầu cơ sở (hoặc người được ủy quyền/đội trưởng theo quy định)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Bất kỳ ai có mặt</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Người dân gần nhất</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Tổ trưởng dân phố bắt buộc</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, khi cháy phương tiện giao thông đang lưu thông, ai là người chỉ huy chữa cháy khi lực lượng Công an chưa đến?</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Người chỉ huy phương tiện/chủ phương tiện; nếu vắng mặt thì người điều khiển phương tiện</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Hành khách bất kỳ</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh sát giao thông</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Tổ trưởng dân phố</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Bảo vệ hiện trường, điều tra vụ cháy thuộc trách nhiệm chính của cơ quan nào theo Luật 2024?</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan Công an</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>UBND cấp xã</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan y tế</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan điện lực</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Điều 30 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan/tổ chức/hộ gia đình/cá nhân nơi xảy ra cháy có trách nhiệm gì liên quan đến hiện trường vụ cháy?</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Tham gia bảo vệ hiện trường, cung cấp thông tin xác thực cho cơ quan Công an</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Tự ý dọn dẹp hiện trường</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Cấm lực lượng chức năng tiếp cận</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cung cấp thông tin khi được trả phí</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Điều 30 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Tình huống cứu nạn, cứu hộ theo Luật 2024 bao gồm nội dung nào?</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Cứu nạn, cứu hộ trong đám cháy; trong tai nạn/sự cố; và tìm kiếm nạn nhân</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cứu nạn trong đám cháy</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cứu nạn giao thông</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tìm kiếm nạn nhân</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Điều 32 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, tình huống tai nạn, sự cố cần CNCH (điểm b khoản 1 Điều 32) có thể bao gồm trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Có người đuối nước; sập/đổ công trình; sạt lở; tai nạn giao thông đường bộ/đường sắt/đường thủy nội địa; ...</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ đuối nước</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tai nạn hàng không</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cháy rừng</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Điều 32 khoản 1 điểm b. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Người phát hiện tình huống CNCH và người gần nơi xảy ra cháy/tai nạn/sự cố có trách nhiệm gì?</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Tham gia cứu nạn, cứu hộ trong điều kiện, khả năng cho phép</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Không được tham gia dưới mọi hình thức</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tham gia nếu có hợp đồng</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tham gia khi có cháy</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Điều 33 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Khi xảy ra cháy cần CNCH, ai là người chỉ huy cứu nạn, cứu hộ?</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Người chỉ huy chữa cháy thuộc lực lượng Công an nhân dân</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chủ tịch UBND cấp xã</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Bất kỳ cán bộ y tế nào có mặt</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Trưởng thôn</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Điều 34 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, lực lượng phòng cháy, chữa cháy và cứu nạn, cứu hộ gồm những lực lượng nào?</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Cảnh sát PCCC &amp; CNCH; lực lượng PCCC &amp; CNCH cơ sở; chuyên ngành; dân phòng</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cảnh sát PCCC &amp; CNCH</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ lực lượng dân phòng</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ lực lượng cơ sở</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Điều 36 khoản 1-4. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Cơ sở đã thành lập Đội PCCC &amp; CNCH chuyên ngành thì có phải thành lập Đội PCCC &amp; CNCH cơ sở không?</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Không phải thành lập Đội PCCC &amp; CNCH cơ sở</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Bắt buộc phải lập cả hai đội</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ lập đội dân phòng</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Không có quy định</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Điều 37 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, cá nhân tham gia hoạt động PCCC &amp; CNCH tình nguyện đăng ký với cơ quan nào?</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Công an cấp xã nơi cư trú</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>UBND cấp huyện</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Phòng Lao động - TB&amp;XH</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan điện lực</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Khoản 1 Điều về PCCC &amp; CNCH tình nguyện (trước Điều 40). Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Theo Luật 2024, cơ quan/tổ chức/hộ gia đình/cá nhân đã trang bị phương tiện PCCC &amp; CNCH có trách nhiệm gì?</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Quản lý, sử dụng, bảo quản, bảo dưỡng để sẵn sàng báo cháy/chữa cháy/CNCH</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Được tự ý bỏ không sử dụng</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ bảo quản khi có đoàn kiểm tra</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ dùng khi có cháy lớn</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Điều 43 khoản 2. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Phương tiện PCCC &amp; CNCH sản xuất, lắp ráp trong nước trước khi lưu thông phải đáp ứng yêu cầu nào?</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Bảo đảm chất lượng, đúng tiêu chuẩn công bố áp dụng và quy chuẩn kỹ thuật tương ứng</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần có hóa đơn bán hàng</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ cần tem nhà sản xuất</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Không cần tiêu chuẩn/quy chuẩn</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Điều 44 khoản 1. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Nguồn tài chính bảo đảm cho hoạt động PCCC &amp; CNCH có thể bao gồm nguồn nào?</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Ngân sách nhà nước; nguồn trích từ bảo hiểm cháy nổ bắt buộc; đóng góp/tài trợ; quỹ hợp pháp khác; ...</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ ngân sách nhà nước</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tài trợ của doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ đóng góp tự nguyện</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Điều về nguồn tài chính (trước Điều 50) và Điều 50. Nguồn: https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=173974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
